--- a/data/WP18/WP18_auswertung_abgeordnete.xlsx
+++ b/data/WP18/WP18_auswertung_abgeordnete.xlsx
@@ -1222,7 +1222,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D30" t="n">
         <v>33</v>
@@ -1231,7 +1231,7 @@
         <v>58</v>
       </c>
       <c r="F30" t="n">
-        <v>44.2307692307692</v>
+        <v>44.7619047619048</v>
       </c>
     </row>
     <row r="31">
@@ -2648,13 +2648,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{598267B1-C062-4D22-B5F0-2A9577CB9026}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95543EC6-664D-4F6F-9AB9-87F73BDA6533}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A968B50-A991-4B55-B179-D4C0064DC395}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EBD2D86-D1A8-40BE-8822-E3646F294A5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61537B3-5628-4A2F-B961-A5DFC9381C1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28DEAD1F-2301-4EF2-A903-7CEC52A6D5CC}"/>
 </file>
--- a/data/WP18/WP18_auswertung_abgeordnete.xlsx
+++ b/data/WP18/WP18_auswertung_abgeordnete.xlsx
@@ -53,250 +53,250 @@
     <t xml:space="preserve">Müller-Rech, Franziska</t>
   </si>
   <si>
+    <t xml:space="preserve">Loose, Christian</t>
+  </si>
+  <si>
     <t xml:space="preserve">Schalley, Zacharias</t>
   </si>
   <si>
-    <t xml:space="preserve">Loose, Christian</t>
-  </si>
-  <si>
     <t xml:space="preserve">Witzel, Ralf</t>
   </si>
   <si>
+    <t xml:space="preserve">Keith, Andreas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tritschler, Sven W.</t>
   </si>
   <si>
-    <t xml:space="preserve">Keith, Andreas</t>
+    <t xml:space="preserve">Kapteinat, Lisa-Kristin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPD</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Vincentz, Martin</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapteinat, Lisa-Kristin</t>
+    <t xml:space="preserve">Klute, Thorsten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engin, Dilek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clemens, Carlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Beucker, Hartmut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prof. Dr. Zerbin, Daniel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teschlade, Lena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kampmann, Christina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lürbke, Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Maelzer, Dennis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brockes, Dietmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hafke, Marcel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Höne, Henning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedel, Dirk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schneider, René</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bakum, Rodion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Butschkau, Anja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dudas, Gordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schneider, Susanne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müller-Witt, Elisabeth</t>
   </si>
   <si>
     <t xml:space="preserve">SPD/FDP</t>
   </si>
   <si>
-    <t xml:space="preserve">Engin, Dilek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Beucker, Hartmut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klute, Thorsten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prof. Dr. Zerbin, Daniel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lürbke, Marc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clemens, Carlo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Höne, Henning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brockes, Dietmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hafke, Marcel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kampmann, Christina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wedel, Dirk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Maelzer, Dennis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schneider, René</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dudas, Gordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schneider, Susanne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bakum, Rodion</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rasche, Christof</t>
   </si>
   <si>
+    <t xml:space="preserve">Watermeier, Sebastian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gosewinkel, Silvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moor, Justus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Hartmann, Bastian</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kämmerling, Stefan</t>
   </si>
   <si>
-    <t xml:space="preserve">Müller-Witt, Elisabeth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Hartmann, Bastian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teschlade, Lena</t>
+    <t xml:space="preserve">Müller, Frank</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Blex, Christian</t>
   </si>
   <si>
-    <t xml:space="preserve">Butschkau, Anja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watermeier, Sebastian</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freimuth, Angela</t>
   </si>
   <si>
-    <t xml:space="preserve">Gosewinkel, Silvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moor, Justus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Philipp, Sarah</t>
   </si>
   <si>
     <t xml:space="preserve">Kahle-Hausmann, Julia</t>
   </si>
   <si>
+    <t xml:space="preserve">Vogt, Alexander</t>
+  </si>
+  <si>
     <t xml:space="preserve">Börner, Frank</t>
   </si>
   <si>
+    <t xml:space="preserve">Ott, Jochen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weng, Christina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wolf, Sven</t>
   </si>
   <si>
+    <t xml:space="preserve">Blumenthal, Ina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Durdu, Tülay</t>
   </si>
   <si>
-    <t xml:space="preserve">Müller, Frank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blumenthal, Ina</t>
+    <t xml:space="preserve">Baran, Volkan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirsch, Carolin</t>
   </si>
   <si>
     <t xml:space="preserve">Bongers, Sonja</t>
   </si>
   <si>
-    <t xml:space="preserve">Baran, Volkan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Baer, Alexander</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirsch, Carolin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vogt, Alexander</t>
+    <t xml:space="preserve">Stinka, André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrieshen, Nina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blask, Inge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neumann, Josef</t>
   </si>
   <si>
     <t xml:space="preserve">Dahm, Christian</t>
   </si>
   <si>
-    <t xml:space="preserve">Ott, Jochen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrieshen, Nina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stinka, André</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blask, Inge</t>
+    <t xml:space="preserve">Gebauer, Yvonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siebel, Christin</t>
   </si>
   <si>
     <t xml:space="preserve">Stamm, Christin-Marie</t>
   </si>
   <si>
-    <t xml:space="preserve">Gebauer, Yvonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siebel, Christin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weng, Christina</t>
+    <t xml:space="preserve">Busche, Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stich, Kirsten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zimkeit, Stefan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lüders, Nadja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obrok, Christian</t>
   </si>
   <si>
     <t xml:space="preserve">Sundermann, Frank</t>
   </si>
   <si>
-    <t xml:space="preserve">Busche, Andrea</t>
+    <t xml:space="preserve">Kutschaty, Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stoltze, Ralf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jörg, Wolfgang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock, Ellen</t>
   </si>
   <si>
     <t xml:space="preserve">Bialas, Andreas</t>
   </si>
   <si>
-    <t xml:space="preserve">Obrok, Christian</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cordes, Frederick</t>
   </si>
   <si>
-    <t xml:space="preserve">Stich, Kirsten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kutschaty, Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock, Ellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zimkeit, Stefan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lüders, Nadja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jörg, Wolfgang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stoltze, Ralf</t>
+    <t xml:space="preserve">Falszewski, Benedikt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röckemann, Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yüksel, Serdar</t>
   </si>
   <si>
     <t xml:space="preserve">Ganzke, Hartmut</t>
   </si>
   <si>
+    <t xml:space="preserve">Göddertz, Thomas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prof. Dr. Pinkwart, Andreas</t>
   </si>
   <si>
-    <t xml:space="preserve">Göddertz, Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Röckemann, Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falszewski, Benedikt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neumann, Josef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yüksel, Serdar</t>
+    <t xml:space="preserve">Löcker, Carsten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavena, Anna Teresa</t>
   </si>
   <si>
     <t xml:space="preserve">Meinhardt, Sandy</t>
   </si>
   <si>
-    <t xml:space="preserve">Kavena, Anna Teresa</t>
+    <t xml:space="preserve">Schmeltzer, Rainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nückel, Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Büteführ, Nadja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Löcker, Carsten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nückel, Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schmeltzer, Rainer</t>
   </si>
   <si>
     <t xml:space="preserve">Yetim, Ibrahim</t>
@@ -662,16 +662,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1696</v>
+        <v>1720</v>
       </c>
       <c r="D2" t="n">
-        <v>36.439858490566</v>
+        <v>36.078488372093</v>
       </c>
       <c r="E2" t="n">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="F2" t="n">
-        <v>22.8183962264151</v>
+        <v>24.8255813953488</v>
       </c>
     </row>
     <row r="3">
@@ -682,16 +682,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="D3" t="n">
-        <v>37.7597087378641</v>
+        <v>37.3309608540925</v>
       </c>
       <c r="E3" t="n">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F3" t="n">
-        <v>24.5145631067961</v>
+        <v>25.6227758007117</v>
       </c>
     </row>
     <row r="4">
@@ -702,16 +702,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="D4" t="n">
-        <v>34.8198051948052</v>
+        <v>34.5922480620155</v>
       </c>
       <c r="E4" t="n">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="F4" t="n">
-        <v>20.4545454545455</v>
+        <v>21.7054263565892</v>
       </c>
     </row>
     <row r="5">
@@ -722,16 +722,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D5" t="n">
-        <v>34.1078947368421</v>
+        <v>33.4487179487179</v>
       </c>
       <c r="E5" t="n">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="F5" t="n">
-        <v>24.4736842105263</v>
+        <v>31.2820512820513</v>
       </c>
     </row>
     <row r="6">
@@ -742,16 +742,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D6" t="n">
-        <v>35.737003058104</v>
+        <v>35.2537313432836</v>
       </c>
       <c r="E6" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F6" t="n">
-        <v>32.7217125382263</v>
+        <v>34.6268656716418</v>
       </c>
     </row>
     <row r="7">
@@ -762,16 +762,16 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="D7" t="n">
-        <v>34.1461038961039</v>
+        <v>35.096875</v>
       </c>
       <c r="E7" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F7" t="n">
-        <v>22.0779220779221</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="8">
@@ -782,16 +782,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="D8" t="n">
-        <v>35.4779661016949</v>
+        <v>33.7335423197492</v>
       </c>
       <c r="E8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F8" t="n">
-        <v>20.6779661016949</v>
+        <v>26.3322884012539</v>
       </c>
     </row>
     <row r="9">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>35.3378839590444</v>
+        <v>32.0809061488673</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>31.740614334471</v>
+        <v>42.0711974110032</v>
       </c>
     </row>
     <row r="10">
@@ -822,16 +822,16 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>36.3592592592593</v>
+        <v>33.1866197183099</v>
       </c>
       <c r="E10" t="n">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="F10" t="n">
-        <v>18.5185185185185</v>
+        <v>33.4507042253521</v>
       </c>
     </row>
     <row r="11">
@@ -842,16 +842,16 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="D11" t="n">
-        <v>33.976833976834</v>
+        <v>36.1115107913669</v>
       </c>
       <c r="E11" t="n">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="F11" t="n">
-        <v>30.1158301158301</v>
+        <v>19.4244604316547</v>
       </c>
     </row>
     <row r="12">
@@ -859,39 +859,39 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="D12" t="n">
-        <v>34.0091743119266</v>
+        <v>36.8307086614173</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="F12" t="n">
-        <v>28.8990825688073</v>
+        <v>23.6220472440945</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="D13" t="n">
-        <v>37.811320754717</v>
+        <v>33.9823788546256</v>
       </c>
       <c r="E13" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F13" t="n">
-        <v>22.1698113207547</v>
+        <v>27.7533039647577</v>
       </c>
     </row>
     <row r="14">
@@ -899,379 +899,379 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D14" t="n">
-        <v>33.5353535353535</v>
+        <v>33.3348623853211</v>
       </c>
       <c r="E14" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F14" t="n">
-        <v>31.8181818181818</v>
+        <v>29.8165137614679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D15" t="n">
-        <v>33.3867403314917</v>
+        <v>33.4666666666667</v>
       </c>
       <c r="E15" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F15" t="n">
-        <v>23.2044198895028</v>
+        <v>31.9047619047619</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="D16" t="n">
-        <v>33.2325581395349</v>
+        <v>31.1844660194175</v>
       </c>
       <c r="E16" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>29.6511627906977</v>
+        <v>51.4563106796116</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="D17" t="n">
-        <v>34.810650887574</v>
+        <v>32.7920792079208</v>
       </c>
       <c r="E17" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="F17" t="n">
-        <v>25.4437869822485</v>
+        <v>27.2277227722772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D18" t="n">
-        <v>43.4967320261438</v>
+        <v>34.4971751412429</v>
       </c>
       <c r="E18" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F18" t="n">
-        <v>7.18954248366013</v>
+        <v>26.5536723163842</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D19" t="n">
-        <v>32.5684931506849</v>
+        <v>33.9537572254335</v>
       </c>
       <c r="E19" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="F19" t="n">
-        <v>36.986301369863</v>
+        <v>27.1676300578035</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D20" t="n">
-        <v>33.9300699300699</v>
+        <v>36.7125</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>37.0629370629371</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="D21" t="n">
-        <v>37.8380281690141</v>
+        <v>43.6792452830189</v>
       </c>
       <c r="E21" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F21" t="n">
-        <v>16.9014084507042</v>
+        <v>9.43396226415094</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D22" t="n">
-        <v>42.1449275362319</v>
+        <v>36.5443037974684</v>
       </c>
       <c r="E22" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="F22" t="n">
-        <v>15.9420289855072</v>
+        <v>15.8227848101266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D23" t="n">
-        <v>37.0507246376812</v>
+        <v>36.9271523178808</v>
       </c>
       <c r="E23" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F23" t="n">
-        <v>17.3913043478261</v>
+        <v>22.5165562913907</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D24" t="n">
-        <v>40.1417910447761</v>
+        <v>41.7414965986395</v>
       </c>
       <c r="E24" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
-        <v>24.6268656716418</v>
+        <v>16.3265306122449</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D25" t="n">
-        <v>36.7744360902256</v>
+        <v>33.2307692307692</v>
       </c>
       <c r="E25" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>14.2857142857143</v>
+        <v>44.0559440559441</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D26" t="n">
-        <v>36.168</v>
+        <v>38.3356643356643</v>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>28.6713286713287</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D27" t="n">
-        <v>35.3983739837398</v>
+        <v>35.4558823529412</v>
       </c>
       <c r="E27" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F27" t="n">
-        <v>20.3252032520325</v>
+        <v>25.7352941176471</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C28" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D28" t="n">
-        <v>36.7767857142857</v>
+        <v>33.6279069767442</v>
       </c>
       <c r="E28" t="n">
         <v>93</v>
       </c>
       <c r="F28" t="n">
-        <v>16.9642857142857</v>
+        <v>27.9069767441861</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C29" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D29" t="n">
-        <v>34.6203703703704</v>
+        <v>34.0697674418605</v>
       </c>
       <c r="E29" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F29" t="n">
-        <v>21.2962962962963</v>
+        <v>23.2558139534884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C30" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D30" t="n">
-        <v>33</v>
+        <v>35.0697674418605</v>
       </c>
       <c r="E30" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>44.7619047619048</v>
+        <v>22.4806201550387</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
+        <v>120</v>
+      </c>
+      <c r="D31" t="n">
+        <v>35.6166666666667</v>
+      </c>
+      <c r="E31" t="n">
         <v>97</v>
       </c>
-      <c r="D31" t="n">
-        <v>35.1030927835052</v>
-      </c>
-      <c r="E31" t="n">
-        <v>74</v>
-      </c>
       <c r="F31" t="n">
-        <v>23.7113402061856</v>
+        <v>19.1666666666667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
       <c r="C32" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D32" t="n">
-        <v>38.7765957446808</v>
+        <v>37.7521367521368</v>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F32" t="n">
-        <v>14.8936170212766</v>
+        <v>20.5128205128205</v>
       </c>
     </row>
     <row r="33">
@@ -1279,19 +1279,19 @@
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D33" t="n">
-        <v>32.0561797752809</v>
+        <v>34.0353982300885</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F33" t="n">
-        <v>31.4606741573034</v>
+        <v>42.4778761061947</v>
       </c>
     </row>
     <row r="34">
@@ -1299,19 +1299,19 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C34" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D34" t="n">
-        <v>35.5227272727273</v>
+        <v>35.7363636363636</v>
       </c>
       <c r="E34" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F34" t="n">
-        <v>19.3181818181818</v>
+        <v>27.2727272727273</v>
       </c>
     </row>
     <row r="35">
@@ -1319,19 +1319,19 @@
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C35" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D35" t="n">
-        <v>36.2906976744186</v>
+        <v>33.7706422018349</v>
       </c>
       <c r="E35" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="F35" t="n">
-        <v>26.7441860465116</v>
+        <v>22.0183486238532</v>
       </c>
     </row>
     <row r="36">
@@ -1339,19 +1339,19 @@
         <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C36" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D36" t="n">
-        <v>35.2261904761905</v>
+        <v>38.8095238095238</v>
       </c>
       <c r="E36" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F36" t="n">
-        <v>21.4285714285714</v>
+        <v>21.9047619047619</v>
       </c>
     </row>
     <row r="37">
@@ -1359,19 +1359,19 @@
         <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C37" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D37" t="n">
-        <v>35.8809523809524</v>
+        <v>32.0196078431373</v>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F37" t="n">
-        <v>27.3809523809524</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -1379,19 +1379,19 @@
         <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C38" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D38" t="n">
-        <v>35.3975903614458</v>
+        <v>34.7070707070707</v>
       </c>
       <c r="E38" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F38" t="n">
-        <v>24.0963855421687</v>
+        <v>28.2828282828283</v>
       </c>
     </row>
     <row r="39">
@@ -1399,19 +1399,19 @@
         <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C39" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D39" t="n">
-        <v>33.9873417721519</v>
+        <v>35.0412371134021</v>
       </c>
       <c r="E39" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F39" t="n">
-        <v>21.5189873417722</v>
+        <v>19.5876288659794</v>
       </c>
     </row>
     <row r="40">
@@ -1419,19 +1419,19 @@
         <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D40" t="n">
-        <v>38.445945945946</v>
+        <v>35.4893617021277</v>
       </c>
       <c r="E40" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F40" t="n">
-        <v>24.3243243243243</v>
+        <v>26.5957446808511</v>
       </c>
     </row>
     <row r="41">
@@ -1439,19 +1439,19 @@
         <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C41" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D41" t="n">
-        <v>35.3783783783784</v>
+        <v>34.75</v>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F41" t="n">
-        <v>28.3783783783784</v>
+        <v>29.3478260869565</v>
       </c>
     </row>
     <row r="42">
@@ -1459,19 +1459,19 @@
         <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C42" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D42" t="n">
-        <v>34.7941176470588</v>
+        <v>35.1071428571429</v>
       </c>
       <c r="E42" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>30.952380952381</v>
       </c>
     </row>
     <row r="43">
@@ -1479,19 +1479,19 @@
         <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C43" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>35.5454545454545</v>
+        <v>33.5822784810127</v>
       </c>
       <c r="E43" t="n">
         <v>55</v>
       </c>
       <c r="F43" t="n">
-        <v>16.6666666666667</v>
+        <v>30.379746835443</v>
       </c>
     </row>
     <row r="44">
@@ -1499,19 +1499,19 @@
         <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C44" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>35.3225806451613</v>
+        <v>36.2784810126582</v>
       </c>
       <c r="E44" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F44" t="n">
-        <v>24.1935483870968</v>
+        <v>22.7848101265823</v>
       </c>
     </row>
     <row r="45">
@@ -1519,19 +1519,19 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D45" t="n">
-        <v>32.3571428571429</v>
+        <v>35.2337662337662</v>
       </c>
       <c r="E45" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>46.4285714285714</v>
+        <v>24.6753246753247</v>
       </c>
     </row>
     <row r="46">
@@ -1539,19 +1539,19 @@
         <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C46" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>33.6909090909091</v>
+        <v>32.8701298701299</v>
       </c>
       <c r="E46" t="n">
         <v>43</v>
       </c>
       <c r="F46" t="n">
-        <v>21.8181818181818</v>
+        <v>44.1558441558442</v>
       </c>
     </row>
     <row r="47">
@@ -1559,19 +1559,19 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C47" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D47" t="n">
-        <v>36.9245283018868</v>
+        <v>32.2337662337662</v>
       </c>
       <c r="E47" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>28.3018867924528</v>
+        <v>35.0649350649351</v>
       </c>
     </row>
     <row r="48">
@@ -1579,19 +1579,19 @@
         <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C48" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D48" t="n">
-        <v>31.4230769230769</v>
+        <v>34.68</v>
       </c>
       <c r="E48" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F48" t="n">
-        <v>30.7692307692308</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -1599,19 +1599,19 @@
         <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C49" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D49" t="n">
-        <v>38.7647058823529</v>
+        <v>35.8840579710145</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F49" t="n">
-        <v>17.6470588235294</v>
+        <v>24.6376811594203</v>
       </c>
     </row>
     <row r="50">
@@ -1619,19 +1619,19 @@
         <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D50" t="n">
-        <v>35.2244897959184</v>
+        <v>32.0307692307692</v>
       </c>
       <c r="E50" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F50" t="n">
-        <v>18.3673469387755</v>
+        <v>46.1538461538462</v>
       </c>
     </row>
     <row r="51">
@@ -1639,19 +1639,19 @@
         <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C51" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D51" t="n">
-        <v>32.3829787234043</v>
+        <v>38.5079365079365</v>
       </c>
       <c r="E51" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F51" t="n">
-        <v>40.4255319148936</v>
+        <v>15.8730158730159</v>
       </c>
     </row>
     <row r="52">
@@ -1659,19 +1659,19 @@
         <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C52" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D52" t="n">
-        <v>36.3478260869565</v>
+        <v>32.3114754098361</v>
       </c>
       <c r="E52" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F52" t="n">
-        <v>19.5652173913043</v>
+        <v>40.983606557377</v>
       </c>
     </row>
     <row r="53">
@@ -1679,19 +1679,19 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C53" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>37.5348837209302</v>
+        <v>30.7166666666667</v>
       </c>
       <c r="E53" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F53" t="n">
-        <v>18.6046511627907</v>
+        <v>38.3333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -1699,19 +1699,19 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C54" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D54" t="n">
-        <v>33.2790697674419</v>
+        <v>33.7931034482759</v>
       </c>
       <c r="E54" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F54" t="n">
-        <v>37.2093023255814</v>
+        <v>24.1379310344828</v>
       </c>
     </row>
     <row r="55">
@@ -1719,19 +1719,19 @@
         <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C55" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D55" t="n">
-        <v>36.1951219512195</v>
+        <v>36.3392857142857</v>
       </c>
       <c r="E55" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
-        <v>26.8292682926829</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
@@ -1739,19 +1739,19 @@
         <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C56" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>35.65</v>
+        <v>35.75</v>
       </c>
       <c r="E56" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F56" t="n">
-        <v>22.5</v>
+        <v>29.1666666666667</v>
       </c>
     </row>
     <row r="57">
@@ -1759,16 +1759,16 @@
         <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C57" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>33.2307692307692</v>
+        <v>33.0416666666667</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F57" t="n">
         <v>33.3333333333333</v>
@@ -1779,19 +1779,19 @@
         <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C58" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D58" t="n">
-        <v>34.1351351351351</v>
+        <v>32.0208333333333</v>
       </c>
       <c r="E58" t="n">
         <v>29</v>
       </c>
       <c r="F58" t="n">
-        <v>21.6216216216216</v>
+        <v>39.5833333333333</v>
       </c>
     </row>
     <row r="59">
@@ -1799,19 +1799,19 @@
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C59" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D59" t="n">
-        <v>33.1111111111111</v>
+        <v>37.3404255319149</v>
       </c>
       <c r="E59" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>30.5555555555556</v>
+        <v>25.531914893617</v>
       </c>
     </row>
     <row r="60">
@@ -1819,19 +1819,19 @@
         <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D60" t="n">
-        <v>32.7</v>
+        <v>30.3191489361702</v>
       </c>
       <c r="E60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
-        <v>26.6666666666667</v>
+        <v>48.936170212766</v>
       </c>
     </row>
     <row r="61">
@@ -1839,19 +1839,19 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D61" t="n">
-        <v>32.5</v>
+        <v>34.2142857142857</v>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F61" t="n">
-        <v>36.6666666666667</v>
+        <v>23.8095238095238</v>
       </c>
     </row>
     <row r="62">
@@ -1859,19 +1859,19 @@
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C62" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D62" t="n">
-        <v>39.9310344827586</v>
+        <v>33.5121951219512</v>
       </c>
       <c r="E62" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F62" t="n">
-        <v>3.44827586206897</v>
+        <v>24.390243902439</v>
       </c>
     </row>
     <row r="63">
@@ -1879,19 +1879,19 @@
         <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C63" t="n">
+        <v>40</v>
+      </c>
+      <c r="D63" t="n">
+        <v>35.075</v>
+      </c>
+      <c r="E63" t="n">
         <v>26</v>
       </c>
-      <c r="D63" t="n">
-        <v>36.4230769230769</v>
-      </c>
-      <c r="E63" t="n">
-        <v>20</v>
-      </c>
       <c r="F63" t="n">
-        <v>23.0769230769231</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
@@ -1899,19 +1899,19 @@
         <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C64" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D64" t="n">
-        <v>36.5454545454545</v>
+        <v>34.8285714285714</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
-        <v>18.1818181818182</v>
+        <v>22.8571428571428</v>
       </c>
     </row>
     <row r="65">
@@ -1919,19 +1919,19 @@
         <v>73</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>42.8095238095238</v>
+        <v>33.6470588235294</v>
       </c>
       <c r="E65" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F65" t="n">
-        <v>23.8095238095238</v>
+        <v>32.3529411764706</v>
       </c>
     </row>
     <row r="66">
@@ -1939,19 +1939,19 @@
         <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>35.35</v>
+        <v>34.6451612903226</v>
       </c>
       <c r="E66" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>35</v>
+        <v>22.5806451612903</v>
       </c>
     </row>
     <row r="67">
@@ -1959,19 +1959,19 @@
         <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C67" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D67" t="n">
-        <v>34.8</v>
+        <v>39.9354838709677</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>22.5806451612903</v>
       </c>
     </row>
     <row r="68">
@@ -1979,19 +1979,19 @@
         <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C68" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D68" t="n">
-        <v>34.8421052631579</v>
+        <v>39.9310344827586</v>
       </c>
       <c r="E68" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F68" t="n">
-        <v>15.7894736842105</v>
+        <v>3.44827586206897</v>
       </c>
     </row>
     <row r="69">
@@ -1999,19 +1999,19 @@
         <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C69" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D69" t="n">
-        <v>31.8947368421053</v>
+        <v>34.6785714285714</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F69" t="n">
-        <v>36.8421052631579</v>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="70">
@@ -2019,19 +2019,19 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C70" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D70" t="n">
-        <v>34.4117647058824</v>
+        <v>35.6428571428571</v>
       </c>
       <c r="E70" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F70" t="n">
-        <v>23.5294117647059</v>
+        <v>17.8571428571429</v>
       </c>
     </row>
     <row r="71">
@@ -2039,19 +2039,19 @@
         <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C71" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D71" t="n">
-        <v>37</v>
+        <v>34.7307692307692</v>
       </c>
       <c r="E71" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>12.5</v>
+        <v>26.9230769230769</v>
       </c>
     </row>
     <row r="72">
@@ -2059,19 +2059,19 @@
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C72" t="n">
+        <v>26</v>
+      </c>
+      <c r="D72" t="n">
+        <v>32.2307692307692</v>
+      </c>
+      <c r="E72" t="n">
         <v>15</v>
       </c>
-      <c r="D72" t="n">
-        <v>36.4666666666667</v>
-      </c>
-      <c r="E72" t="n">
-        <v>12</v>
-      </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>42.3076923076923</v>
       </c>
     </row>
     <row r="73">
@@ -2079,19 +2079,19 @@
         <v>81</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
-        <v>37.9333333333333</v>
+        <v>35.8</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
-        <v>6.66666666666667</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -2099,19 +2099,19 @@
         <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D74" t="n">
-        <v>34.5</v>
+        <v>35.12</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F74" t="n">
-        <v>28.5714285714286</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75">
@@ -2119,19 +2119,19 @@
         <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D75" t="n">
-        <v>28</v>
+        <v>32.0434782608696</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>58.3333333333333</v>
+        <v>34.7826086956522</v>
       </c>
     </row>
     <row r="76">
@@ -2139,19 +2139,19 @@
         <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D76" t="n">
-        <v>36.1818181818182</v>
+        <v>36.8571428571429</v>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
-        <v>27.2727272727273</v>
+        <v>4.76190476190477</v>
       </c>
     </row>
     <row r="77">
@@ -2159,19 +2159,19 @@
         <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D77" t="n">
-        <v>37.9090909090909</v>
+        <v>29.95</v>
       </c>
       <c r="E77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
-        <v>9.09090909090909</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -2179,19 +2179,19 @@
         <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
-        <v>32.9</v>
+        <v>33.2631578947368</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F78" t="n">
-        <v>30</v>
+        <v>26.3157894736842</v>
       </c>
     </row>
     <row r="79">
@@ -2199,19 +2199,19 @@
         <v>87</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D79" t="n">
-        <v>29.9</v>
+        <v>34.5789473684211</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F79" t="n">
-        <v>60</v>
+        <v>31.5789473684211</v>
       </c>
     </row>
     <row r="80">
@@ -2219,19 +2219,19 @@
         <v>88</v>
       </c>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D80" t="n">
-        <v>32</v>
+        <v>28.9285714285714</v>
       </c>
       <c r="E80" t="n">
         <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
@@ -2239,19 +2239,19 @@
         <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D81" t="n">
-        <v>32.3333333333333</v>
+        <v>31.5384615384615</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
-        <v>33.3333333333333</v>
+        <v>46.1538461538462</v>
       </c>
     </row>
     <row r="82">
@@ -2259,19 +2259,19 @@
         <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D82" t="n">
-        <v>36</v>
+        <v>32.9166666666667</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
-        <v>20</v>
+        <v>41.6666666666667</v>
       </c>
     </row>
     <row r="83">
@@ -2279,19 +2279,19 @@
         <v>91</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>24</v>
+        <v>33.2727272727273</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>18.1818181818182</v>
       </c>
     </row>
     <row r="84">
@@ -2299,19 +2299,19 @@
         <v>92</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>29.6666666666667</v>
+        <v>32.2857142857143</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
-        <v>66.6666666666667</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="85">
@@ -2322,13 +2322,13 @@
         <v>11</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>43.3333333333333</v>
+        <v>34.3333333333333</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2339,19 +2339,19 @@
         <v>94</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>29.5</v>
+        <v>26</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
@@ -2359,19 +2359,19 @@
         <v>95</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>28</v>
+        <v>30.6</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88">
@@ -2399,7 +2399,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -2648,13 +2648,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95543EC6-664D-4F6F-9AB9-87F73BDA6533}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22236C4D-629A-435A-B17E-AD737C32F4A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EBD2D86-D1A8-40BE-8822-E3646F294A5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F999C80-11DB-4435-A0A7-E60AAB628372}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28DEAD1F-2301-4EF2-A903-7CEC52A6D5CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DDEBD98-E0EC-4DC9-B62C-AE24356B9607}"/>
 </file>
--- a/data/WP18/WP18_auswertung_abgeordnete.xlsx
+++ b/data/WP18/WP18_auswertung_abgeordnete.xlsx
@@ -668,10 +668,10 @@
         <v>36.078488372093</v>
       </c>
       <c r="E2" t="n">
-        <v>1293</v>
+        <v>1397</v>
       </c>
       <c r="F2" t="n">
-        <v>24.8255813953488</v>
+        <v>18.7790697674419</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         <v>37.3309608540925</v>
       </c>
       <c r="E3" t="n">
-        <v>627</v>
+        <v>669</v>
       </c>
       <c r="F3" t="n">
-        <v>25.6227758007117</v>
+        <v>20.6405693950178</v>
       </c>
     </row>
     <row r="4">
@@ -708,10 +708,10 @@
         <v>34.5922480620155</v>
       </c>
       <c r="E4" t="n">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="F4" t="n">
-        <v>21.7054263565892</v>
+        <v>17.6744186046512</v>
       </c>
     </row>
     <row r="5">
@@ -728,10 +728,10 @@
         <v>33.4487179487179</v>
       </c>
       <c r="E5" t="n">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="F5" t="n">
-        <v>31.2820512820513</v>
+        <v>23.8461538461539</v>
       </c>
     </row>
     <row r="6">
@@ -748,10 +748,10 @@
         <v>35.2537313432836</v>
       </c>
       <c r="E6" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="F6" t="n">
-        <v>34.6268656716418</v>
+        <v>30.1492537313433</v>
       </c>
     </row>
     <row r="7">
@@ -768,10 +768,10 @@
         <v>35.096875</v>
       </c>
       <c r="E7" t="n">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="F7" t="n">
-        <v>22.5</v>
+        <v>15.3125</v>
       </c>
     </row>
     <row r="8">
@@ -788,10 +788,10 @@
         <v>33.7335423197492</v>
       </c>
       <c r="E8" t="n">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="F8" t="n">
-        <v>26.3322884012539</v>
+        <v>20.3761755485893</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>32.0809061488673</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="F9" t="n">
-        <v>42.0711974110032</v>
+        <v>33.6569579288026</v>
       </c>
     </row>
     <row r="10">
@@ -828,10 +828,10 @@
         <v>33.1866197183099</v>
       </c>
       <c r="E10" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="F10" t="n">
-        <v>33.4507042253521</v>
+        <v>26.7605633802817</v>
       </c>
     </row>
     <row r="11">
@@ -848,10 +848,10 @@
         <v>36.1115107913669</v>
       </c>
       <c r="E11" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F11" t="n">
-        <v>19.4244604316547</v>
+        <v>16.1870503597122</v>
       </c>
     </row>
     <row r="12">
@@ -868,10 +868,10 @@
         <v>36.8307086614173</v>
       </c>
       <c r="E12" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F12" t="n">
-        <v>23.6220472440945</v>
+        <v>19.6850393700787</v>
       </c>
     </row>
     <row r="13">
@@ -888,10 +888,10 @@
         <v>33.9823788546256</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F13" t="n">
-        <v>27.7533039647577</v>
+        <v>22.9074889867841</v>
       </c>
     </row>
     <row r="14">
@@ -908,10 +908,10 @@
         <v>33.3348623853211</v>
       </c>
       <c r="E14" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F14" t="n">
-        <v>29.8165137614679</v>
+        <v>24.3119266055046</v>
       </c>
     </row>
     <row r="15">
@@ -928,10 +928,10 @@
         <v>33.4666666666667</v>
       </c>
       <c r="E15" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F15" t="n">
-        <v>31.9047619047619</v>
+        <v>24.7619047619048</v>
       </c>
     </row>
     <row r="16">
@@ -948,10 +948,10 @@
         <v>31.1844660194175</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F16" t="n">
-        <v>51.4563106796116</v>
+        <v>45.1456310679612</v>
       </c>
     </row>
     <row r="17">
@@ -968,10 +968,10 @@
         <v>32.7920792079208</v>
       </c>
       <c r="E17" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F17" t="n">
-        <v>27.2277227722772</v>
+        <v>21.2871287128713</v>
       </c>
     </row>
     <row r="18">
@@ -988,10 +988,10 @@
         <v>34.4971751412429</v>
       </c>
       <c r="E18" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F18" t="n">
-        <v>26.5536723163842</v>
+        <v>14.1242937853107</v>
       </c>
     </row>
     <row r="19">
@@ -1008,10 +1008,10 @@
         <v>33.9537572254335</v>
       </c>
       <c r="E19" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F19" t="n">
-        <v>27.1676300578035</v>
+        <v>16.7630057803468</v>
       </c>
     </row>
     <row r="20">
@@ -1028,10 +1028,10 @@
         <v>36.7125</v>
       </c>
       <c r="E20" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F20" t="n">
-        <v>18.75</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="21">
@@ -1048,10 +1048,10 @@
         <v>43.6792452830189</v>
       </c>
       <c r="E21" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F21" t="n">
-        <v>9.43396226415094</v>
+        <v>8.80503144654088</v>
       </c>
     </row>
     <row r="22">
@@ -1068,10 +1068,10 @@
         <v>36.5443037974684</v>
       </c>
       <c r="E22" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F22" t="n">
-        <v>15.8227848101266</v>
+        <v>12.0253164556962</v>
       </c>
     </row>
     <row r="23">
@@ -1088,10 +1088,10 @@
         <v>36.9271523178808</v>
       </c>
       <c r="E23" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F23" t="n">
-        <v>22.5165562913907</v>
+        <v>15.8940397350993</v>
       </c>
     </row>
     <row r="24">
@@ -1108,10 +1108,10 @@
         <v>41.7414965986395</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" t="n">
-        <v>16.3265306122449</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="25">
@@ -1128,10 +1128,10 @@
         <v>33.2307692307692</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>44.0559440559441</v>
+        <v>37.7622377622378</v>
       </c>
     </row>
     <row r="26">
@@ -1148,10 +1148,10 @@
         <v>38.3356643356643</v>
       </c>
       <c r="E26" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F26" t="n">
-        <v>28.6713286713287</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="27">
@@ -1168,10 +1168,10 @@
         <v>35.4558823529412</v>
       </c>
       <c r="E27" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F27" t="n">
-        <v>25.7352941176471</v>
+        <v>20.5882352941177</v>
       </c>
     </row>
     <row r="28">
@@ -1188,10 +1188,10 @@
         <v>33.6279069767442</v>
       </c>
       <c r="E28" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F28" t="n">
-        <v>27.9069767441861</v>
+        <v>20.1550387596899</v>
       </c>
     </row>
     <row r="29">
@@ -1208,10 +1208,10 @@
         <v>34.0697674418605</v>
       </c>
       <c r="E29" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F29" t="n">
-        <v>23.2558139534884</v>
+        <v>16.2790697674419</v>
       </c>
     </row>
     <row r="30">
@@ -1228,10 +1228,10 @@
         <v>35.0697674418605</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F30" t="n">
-        <v>22.4806201550387</v>
+        <v>17.8294573643411</v>
       </c>
     </row>
     <row r="31">
@@ -1248,10 +1248,10 @@
         <v>35.6166666666667</v>
       </c>
       <c r="E31" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F31" t="n">
-        <v>19.1666666666667</v>
+        <v>15.8333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -1268,10 +1268,10 @@
         <v>37.7521367521368</v>
       </c>
       <c r="E32" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F32" t="n">
-        <v>20.5128205128205</v>
+        <v>12.8205128205128</v>
       </c>
     </row>
     <row r="33">
@@ -1288,10 +1288,10 @@
         <v>34.0353982300885</v>
       </c>
       <c r="E33" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F33" t="n">
-        <v>42.4778761061947</v>
+        <v>38.9380530973451</v>
       </c>
     </row>
     <row r="34">
@@ -1308,10 +1308,10 @@
         <v>35.7363636363636</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F34" t="n">
-        <v>27.2727272727273</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1328,10 +1328,10 @@
         <v>33.7706422018349</v>
       </c>
       <c r="E35" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F35" t="n">
-        <v>22.0183486238532</v>
+        <v>18.348623853211</v>
       </c>
     </row>
     <row r="36">
@@ -1348,10 +1348,10 @@
         <v>38.8095238095238</v>
       </c>
       <c r="E36" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F36" t="n">
-        <v>21.9047619047619</v>
+        <v>18.0952380952381</v>
       </c>
     </row>
     <row r="37">
@@ -1368,10 +1368,10 @@
         <v>32.0196078431373</v>
       </c>
       <c r="E37" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F37" t="n">
-        <v>33.3333333333333</v>
+        <v>27.4509803921569</v>
       </c>
     </row>
     <row r="38">
@@ -1388,10 +1388,10 @@
         <v>34.7070707070707</v>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F38" t="n">
-        <v>28.2828282828283</v>
+        <v>19.1919191919192</v>
       </c>
     </row>
     <row r="39">
@@ -1408,10 +1408,10 @@
         <v>35.0412371134021</v>
       </c>
       <c r="E39" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F39" t="n">
-        <v>19.5876288659794</v>
+        <v>12.3711340206186</v>
       </c>
     </row>
     <row r="40">
@@ -1428,10 +1428,10 @@
         <v>35.4893617021277</v>
       </c>
       <c r="E40" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F40" t="n">
-        <v>26.5957446808511</v>
+        <v>19.1489361702128</v>
       </c>
     </row>
     <row r="41">
@@ -1448,10 +1448,10 @@
         <v>34.75</v>
       </c>
       <c r="E41" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F41" t="n">
-        <v>29.3478260869565</v>
+        <v>28.2608695652174</v>
       </c>
     </row>
     <row r="42">
@@ -1468,10 +1468,10 @@
         <v>35.1071428571429</v>
       </c>
       <c r="E42" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F42" t="n">
-        <v>30.952380952381</v>
+        <v>21.4285714285714</v>
       </c>
     </row>
     <row r="43">
@@ -1488,10 +1488,10 @@
         <v>33.5822784810127</v>
       </c>
       <c r="E43" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>30.379746835443</v>
+        <v>24.0506329113924</v>
       </c>
     </row>
     <row r="44">
@@ -1508,10 +1508,10 @@
         <v>36.2784810126582</v>
       </c>
       <c r="E44" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F44" t="n">
-        <v>22.7848101265823</v>
+        <v>18.9873417721519</v>
       </c>
     </row>
     <row r="45">
@@ -1528,10 +1528,10 @@
         <v>35.2337662337662</v>
       </c>
       <c r="E45" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F45" t="n">
-        <v>24.6753246753247</v>
+        <v>19.4805194805195</v>
       </c>
     </row>
     <row r="46">
@@ -1548,10 +1548,10 @@
         <v>32.8701298701299</v>
       </c>
       <c r="E46" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F46" t="n">
-        <v>44.1558441558442</v>
+        <v>22.0779220779221</v>
       </c>
     </row>
     <row r="47">
@@ -1568,10 +1568,10 @@
         <v>32.2337662337662</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F47" t="n">
-        <v>35.0649350649351</v>
+        <v>27.2727272727273</v>
       </c>
     </row>
     <row r="48">
@@ -1588,10 +1588,10 @@
         <v>34.68</v>
       </c>
       <c r="E48" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>17.3333333333333</v>
       </c>
     </row>
     <row r="49">
@@ -1608,10 +1608,10 @@
         <v>35.8840579710145</v>
       </c>
       <c r="E49" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F49" t="n">
-        <v>24.6376811594203</v>
+        <v>20.2898550724638</v>
       </c>
     </row>
     <row r="50">
@@ -1628,10 +1628,10 @@
         <v>32.0307692307692</v>
       </c>
       <c r="E50" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>46.1538461538462</v>
+        <v>29.2307692307692</v>
       </c>
     </row>
     <row r="51">
@@ -1648,10 +1648,10 @@
         <v>38.5079365079365</v>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F51" t="n">
-        <v>15.8730158730159</v>
+        <v>12.6984126984127</v>
       </c>
     </row>
     <row r="52">
@@ -1668,10 +1668,10 @@
         <v>32.3114754098361</v>
       </c>
       <c r="E52" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>40.983606557377</v>
+        <v>18.0327868852459</v>
       </c>
     </row>
     <row r="53">
@@ -1688,10 +1688,10 @@
         <v>30.7166666666667</v>
       </c>
       <c r="E53" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F53" t="n">
-        <v>38.3333333333333</v>
+        <v>28.3333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -1708,10 +1708,10 @@
         <v>33.7931034482759</v>
       </c>
       <c r="E54" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F54" t="n">
-        <v>24.1379310344828</v>
+        <v>17.2413793103448</v>
       </c>
     </row>
     <row r="55">
@@ -1728,10 +1728,10 @@
         <v>36.3392857142857</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>23.2142857142857</v>
       </c>
     </row>
     <row r="56">
@@ -1748,10 +1748,10 @@
         <v>35.75</v>
       </c>
       <c r="E56" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>29.1666666666667</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -1768,10 +1768,10 @@
         <v>33.0416666666667</v>
       </c>
       <c r="E57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>33.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
@@ -1788,10 +1788,10 @@
         <v>32.0208333333333</v>
       </c>
       <c r="E58" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F58" t="n">
-        <v>39.5833333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
@@ -1808,10 +1808,10 @@
         <v>37.3404255319149</v>
       </c>
       <c r="E59" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F59" t="n">
-        <v>25.531914893617</v>
+        <v>17.0212765957447</v>
       </c>
     </row>
     <row r="60">
@@ -1828,10 +1828,10 @@
         <v>30.3191489361702</v>
       </c>
       <c r="E60" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F60" t="n">
-        <v>48.936170212766</v>
+        <v>40.4255319148936</v>
       </c>
     </row>
     <row r="61">
@@ -1848,10 +1848,10 @@
         <v>34.2142857142857</v>
       </c>
       <c r="E61" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61" t="n">
-        <v>23.8095238095238</v>
+        <v>21.4285714285714</v>
       </c>
     </row>
     <row r="62">
@@ -1868,10 +1868,10 @@
         <v>33.5121951219512</v>
       </c>
       <c r="E62" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>24.390243902439</v>
+        <v>14.6341463414634</v>
       </c>
     </row>
     <row r="63">
@@ -1888,10 +1888,10 @@
         <v>35.075</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F63" t="n">
-        <v>35</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="64">
@@ -1908,10 +1908,10 @@
         <v>34.8285714285714</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F64" t="n">
-        <v>22.8571428571428</v>
+        <v>11.4285714285714</v>
       </c>
     </row>
     <row r="65">
@@ -1928,10 +1928,10 @@
         <v>33.6470588235294</v>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F65" t="n">
-        <v>32.3529411764706</v>
+        <v>20.5882352941177</v>
       </c>
     </row>
     <row r="66">
@@ -1948,10 +1948,10 @@
         <v>34.6451612903226</v>
       </c>
       <c r="E66" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F66" t="n">
-        <v>22.5806451612903</v>
+        <v>16.1290322580645</v>
       </c>
     </row>
     <row r="67">
@@ -1968,10 +1968,10 @@
         <v>39.9354838709677</v>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F67" t="n">
-        <v>22.5806451612903</v>
+        <v>16.1290322580645</v>
       </c>
     </row>
     <row r="68">
@@ -2008,10 +2008,10 @@
         <v>34.6785714285714</v>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F69" t="n">
-        <v>28.5714285714286</v>
+        <v>17.8571428571429</v>
       </c>
     </row>
     <row r="70">
@@ -2028,10 +2028,10 @@
         <v>35.6428571428571</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
-        <v>17.8571428571429</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="71">
@@ -2048,10 +2048,10 @@
         <v>34.7307692307692</v>
       </c>
       <c r="E71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F71" t="n">
-        <v>26.9230769230769</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="72">
@@ -2068,10 +2068,10 @@
         <v>32.2307692307692</v>
       </c>
       <c r="E72" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F72" t="n">
-        <v>42.3076923076923</v>
+        <v>26.9230769230769</v>
       </c>
     </row>
     <row r="73">
@@ -2088,10 +2088,10 @@
         <v>35.8</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -2108,10 +2108,10 @@
         <v>35.12</v>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F74" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
@@ -2128,10 +2128,10 @@
         <v>32.0434782608696</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F75" t="n">
-        <v>34.7826086956522</v>
+        <v>21.7391304347826</v>
       </c>
     </row>
     <row r="76">
@@ -2168,10 +2168,10 @@
         <v>29.95</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
@@ -2188,10 +2188,10 @@
         <v>33.2631578947368</v>
       </c>
       <c r="E78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>26.3157894736842</v>
+        <v>21.0526315789474</v>
       </c>
     </row>
     <row r="79">
@@ -2208,10 +2208,10 @@
         <v>34.5789473684211</v>
       </c>
       <c r="E79" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>31.5789473684211</v>
+        <v>21.0526315789474</v>
       </c>
     </row>
     <row r="80">
@@ -2228,10 +2228,10 @@
         <v>28.9285714285714</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>50</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="81">
@@ -2248,10 +2248,10 @@
         <v>31.5384615384615</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>46.1538461538462</v>
+        <v>30.7692307692308</v>
       </c>
     </row>
     <row r="82">
@@ -2268,10 +2268,10 @@
         <v>32.9166666666667</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>41.6666666666667</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -2348,10 +2348,10 @@
         <v>26</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
@@ -2368,10 +2368,10 @@
         <v>30.6</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88">
@@ -2648,13 +2648,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22236C4D-629A-435A-B17E-AD737C32F4A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1E76A5C-5762-4419-BAEF-FA4F7014E86F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F999C80-11DB-4435-A0A7-E60AAB628372}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DCBDBC0-4F12-49F1-83F5-4D64596D2717}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DDEBD98-E0EC-4DC9-B62C-AE24356B9607}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8618ABC-C07D-4F9C-9D76-71D3BF836DDA}"/>
 </file>